--- a/data/shock_index.xlsx
+++ b/data/shock_index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_R\practical_stats_med-r\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_R\bookdown-crc-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C94AAF-75A2-48BF-89B8-18832F2D9F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F257A9-802B-4900-8607-15913B3A23C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,15 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="6">
   <si>
-    <t>sex</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>sbp</t>
-  </si>
-  <si>
     <t>HR</t>
   </si>
   <si>
@@ -38,6 +29,15 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>SBP</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>Age</t>
   </si>
 </sst>
 </file>
@@ -395,21 +395,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>54</v>
@@ -423,7 +423,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>47</v>
@@ -437,21 +437,21 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>58</v>
       </c>
       <c r="C4">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D4">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>170</v>
@@ -462,7 +462,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6">
         <v>60</v>
@@ -476,7 +476,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7">
         <v>57</v>
@@ -490,21 +490,21 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B8">
         <v>54</v>
       </c>
       <c r="C8">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D8">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>53</v>
@@ -529,7 +529,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>58</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B12">
         <v>49</v>
@@ -557,7 +557,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B13">
         <v>55</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B14">
         <v>57</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B15">
         <v>52</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B16">
         <v>50</v>
@@ -613,7 +613,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B17">
         <v>48</v>
@@ -627,7 +627,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B18">
         <v>56</v>
@@ -641,7 +641,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B19">
         <v>54</v>
@@ -655,7 +655,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B20">
         <v>59</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B21">
         <v>56</v>
@@ -683,7 +683,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B22">
         <v>48</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B23">
         <v>52</v>
@@ -711,7 +711,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B24">
         <v>55</v>
@@ -725,7 +725,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B25">
         <v>57</v>
@@ -739,7 +739,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B26">
         <v>58</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B27">
         <v>48</v>
@@ -767,7 +767,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B28">
         <v>55</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B29">
         <v>59</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B30">
         <v>48</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B31">
         <v>51</v>
